--- a/data/trans_orig/IQ18C_M-Clase-trans_orig.xlsx
+++ b/data/trans_orig/IQ18C_M-Clase-trans_orig.xlsx
@@ -526,7 +526,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Tiempo que dura el trayecto desde su domicilio al médico en minutos</t>
+          <t>Tiempo que dura el trayecto desde su domicilio al médico en minutos (tasa de respuesta: 95,27%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -716,62 +716,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>13,97; 16,42</t>
+          <t>13,92; 16,37</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>10,27; 13,44</t>
+          <t>10,34; 13,37</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>11,17; 14,24</t>
+          <t>11,18; 14,15</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>11,77; 18,46</t>
+          <t>11,68; 18,39</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>13,67; 16,8</t>
+          <t>13,55; 16,66</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>11,6; 14,26</t>
+          <t>11,54; 14,13</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>10,46; 13,18</t>
+          <t>10,45; 13,22</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>9,3; 14,2</t>
+          <t>9,44; 13,94</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>14,07; 16,08</t>
+          <t>14,08; 16,02</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>11,34; 13,39</t>
+          <t>11,27; 13,2</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>11,05; 13,04</t>
+          <t>11,1; 13,16</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>11,27; 15,38</t>
+          <t>11,2; 15,55</t>
         </is>
       </c>
     </row>
@@ -856,62 +856,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>13,17; 15,88</t>
+          <t>13,16; 15,93</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>10,54; 12,89</t>
+          <t>10,57; 12,89</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>10,62; 13,75</t>
+          <t>10,64; 13,79</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>7,19; 14,43</t>
+          <t>6,96; 13,96</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>12,24; 16,37</t>
+          <t>12,15; 16,16</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>11,51; 15,45</t>
+          <t>11,47; 15,37</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>11,31; 14,32</t>
+          <t>11,19; 14,26</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>10,27; 15,68</t>
+          <t>10,49; 15,65</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>13,08; 15,42</t>
+          <t>13,12; 15,54</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>11,34; 13,63</t>
+          <t>11,36; 13,56</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>11,16; 13,43</t>
+          <t>11,29; 13,49</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>9,82; 14,11</t>
+          <t>9,51; 13,98</t>
         </is>
       </c>
     </row>
@@ -996,62 +996,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>12,53; 14,88</t>
+          <t>12,45; 14,89</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>10,55; 13,56</t>
+          <t>10,49; 13,61</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>10,19; 12,74</t>
+          <t>10,16; 12,74</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>6,0; 14,41</t>
+          <t>6,29; 14,45</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>13,3; 16,43</t>
+          <t>13,28; 16,52</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>10,08; 13,21</t>
+          <t>10,19; 13,47</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>10,84; 13,77</t>
+          <t>10,84; 13,73</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>12,2; 30,14</t>
+          <t>12,14; 31,26</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>13,26; 15,26</t>
+          <t>13,18; 15,21</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>10,66; 12,78</t>
+          <t>10,6; 12,82</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>10,85; 12,77</t>
+          <t>10,92; 12,84</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>11,46; 27,08</t>
+          <t>11,77; 27,68</t>
         </is>
       </c>
     </row>
@@ -1136,62 +1136,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>12,73; 14,39</t>
+          <t>12,8; 14,44</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>11,29; 13,85</t>
+          <t>11,28; 13,69</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>10,64; 12,25</t>
+          <t>10,64; 12,37</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>9,67; 16,65</t>
+          <t>9,65; 16,86</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>12,53; 14,02</t>
+          <t>12,55; 14,06</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>10,42; 12,27</t>
+          <t>10,38; 12,27</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>10,63; 12,49</t>
+          <t>10,56; 12,48</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>11,0; 14,82</t>
+          <t>10,79; 14,78</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>12,86; 14,0</t>
+          <t>12,86; 13,93</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>11,02; 12,56</t>
+          <t>11,0; 12,52</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>10,87; 12,21</t>
+          <t>10,85; 12,05</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>11,01; 14,85</t>
+          <t>11,04; 14,97</t>
         </is>
       </c>
     </row>
@@ -1276,62 +1276,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>12,5; 16,15</t>
+          <t>12,55; 16,27</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>9,81; 11,69</t>
+          <t>9,84; 11,55</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>10,31; 12,81</t>
+          <t>10,35; 12,79</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>12,5; 31,37</t>
+          <t>12,4; 30,47</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>12,45; 15,09</t>
+          <t>12,4; 15,32</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>11,11; 14,0</t>
+          <t>10,99; 13,72</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>10,54; 13,59</t>
+          <t>10,5; 13,68</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>9,2; 16,02</t>
+          <t>9,18; 15,63</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>12,73; 14,92</t>
+          <t>12,74; 14,8</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>10,62; 12,42</t>
+          <t>10,66; 12,3</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>10,76; 12,84</t>
+          <t>10,74; 12,8</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>11,31; 19,44</t>
+          <t>11,29; 19,31</t>
         </is>
       </c>
     </row>
@@ -1416,62 +1416,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>13,22; 15,93</t>
+          <t>13,19; 16,07</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>12,43; 18,06</t>
+          <t>12,42; 17,53</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>10,17; 13,92</t>
+          <t>10,21; 13,7</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>9,29; 15,91</t>
+          <t>9,57; 15,99</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>12,57; 16,27</t>
+          <t>12,47; 16,4</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>10,83; 14,1</t>
+          <t>10,89; 14,13</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>10,28; 14,07</t>
+          <t>10,35; 13,67</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>9,24; 21,74</t>
+          <t>8,67; 20,86</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>13,27; 15,52</t>
+          <t>13,32; 15,63</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>11,89; 14,64</t>
+          <t>11,95; 14,8</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>10,63; 13,16</t>
+          <t>10,49; 13,02</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>10,18; 17,5</t>
+          <t>10,33; 17,8</t>
         </is>
       </c>
     </row>
@@ -1556,62 +1556,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>13,6; 14,61</t>
+          <t>13,58; 14,61</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>11,38; 12,54</t>
+          <t>11,37; 12,44</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>11,07; 12,13</t>
+          <t>11,09; 12,16</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>12,02; 16,64</t>
+          <t>12,01; 16,53</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>13,32; 14,48</t>
+          <t>13,36; 14,42</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>11,38; 12,57</t>
+          <t>11,43; 12,51</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>11,28; 12,36</t>
+          <t>11,31; 12,41</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>11,57; 14,41</t>
+          <t>11,58; 14,27</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>13,58; 14,35</t>
+          <t>13,59; 14,36</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>11,52; 12,3</t>
+          <t>11,54; 12,32</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>11,33; 12,09</t>
+          <t>11,34; 12,12</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>12,22; 14,74</t>
+          <t>12,08; 14,76</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/IQ18C_M-Clase-trans_orig.xlsx
+++ b/data/trans_orig/IQ18C_M-Clase-trans_orig.xlsx
@@ -716,62 +716,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>13,92; 16,37</t>
+          <t>13,81; 16,28</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>10,34; 13,37</t>
+          <t>10,39; 13,39</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>11,18; 14,15</t>
+          <t>11,2; 14,12</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>11,68; 18,39</t>
+          <t>11,87; 18,85</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>13,55; 16,66</t>
+          <t>13,6; 16,72</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>11,54; 14,13</t>
+          <t>11,48; 14,15</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>10,45; 13,22</t>
+          <t>10,51; 13,33</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>9,44; 13,94</t>
+          <t>9,35; 14,38</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>14,08; 16,02</t>
+          <t>14,03; 16,02</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>11,27; 13,2</t>
+          <t>11,21; 13,32</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>11,1; 13,16</t>
+          <t>11,05; 13,07</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>11,2; 15,55</t>
+          <t>11,11; 15,4</t>
         </is>
       </c>
     </row>
@@ -856,62 +856,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>13,16; 15,93</t>
+          <t>13,25; 15,94</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>10,57; 12,89</t>
+          <t>10,57; 12,97</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>10,64; 13,79</t>
+          <t>10,71; 14,03</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>6,96; 13,96</t>
+          <t>6,77; 14,11</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>12,15; 16,16</t>
+          <t>12,2; 16,2</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>11,47; 15,37</t>
+          <t>11,55; 15,75</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>11,19; 14,26</t>
+          <t>11,31; 14,24</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>10,49; 15,65</t>
+          <t>10,51; 15,86</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>13,12; 15,54</t>
+          <t>13,01; 15,34</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>11,36; 13,56</t>
+          <t>11,33; 13,56</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>11,29; 13,49</t>
+          <t>11,26; 13,49</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>9,51; 13,98</t>
+          <t>9,72; 13,95</t>
         </is>
       </c>
     </row>
@@ -996,62 +996,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>12,45; 14,89</t>
+          <t>12,47; 14,84</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>10,49; 13,61</t>
+          <t>10,43; 13,68</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>10,16; 12,74</t>
+          <t>10,16; 12,77</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>6,29; 14,45</t>
+          <t>5,57; 14,4</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>13,28; 16,52</t>
+          <t>13,22; 16,42</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>10,19; 13,47</t>
+          <t>10,28; 13,49</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>10,84; 13,73</t>
+          <t>10,89; 13,6</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>12,14; 31,26</t>
+          <t>12,01; 31,48</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>13,18; 15,21</t>
+          <t>13,17; 15,25</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>10,6; 12,82</t>
+          <t>10,65; 12,75</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>10,92; 12,84</t>
+          <t>10,78; 12,81</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>11,77; 27,68</t>
+          <t>11,56; 26,49</t>
         </is>
       </c>
     </row>
@@ -1136,62 +1136,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>12,8; 14,44</t>
+          <t>12,78; 14,34</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>11,28; 13,69</t>
+          <t>11,41; 13,94</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>10,64; 12,37</t>
+          <t>10,64; 12,38</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>9,65; 16,86</t>
+          <t>9,68; 17,03</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>12,55; 14,06</t>
+          <t>12,52; 14,01</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>10,38; 12,27</t>
+          <t>10,35; 12,23</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>10,56; 12,48</t>
+          <t>10,65; 12,61</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>10,79; 14,78</t>
+          <t>10,93; 15,03</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>12,86; 13,93</t>
+          <t>12,86; 13,98</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>11,0; 12,52</t>
+          <t>11,03; 12,57</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>10,85; 12,05</t>
+          <t>10,83; 12,11</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>11,04; 14,97</t>
+          <t>10,8; 15,06</t>
         </is>
       </c>
     </row>
@@ -1276,62 +1276,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>12,55; 16,27</t>
+          <t>12,55; 16,23</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>9,84; 11,55</t>
+          <t>9,85; 11,64</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>10,35; 12,79</t>
+          <t>10,29; 12,69</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>12,4; 30,47</t>
+          <t>12,6; 29,66</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>12,4; 15,32</t>
+          <t>12,46; 15,11</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>10,99; 13,72</t>
+          <t>11,05; 13,89</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>10,5; 13,68</t>
+          <t>10,52; 13,7</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>9,18; 15,63</t>
+          <t>9,17; 15,39</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>12,74; 14,8</t>
+          <t>12,76; 14,97</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>10,66; 12,3</t>
+          <t>10,68; 12,36</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>10,74; 12,8</t>
+          <t>10,72; 12,6</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>11,29; 19,31</t>
+          <t>11,1; 18,86</t>
         </is>
       </c>
     </row>
@@ -1416,62 +1416,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>13,19; 16,07</t>
+          <t>13,21; 15,87</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>12,42; 17,53</t>
+          <t>12,31; 17,41</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>10,21; 13,7</t>
+          <t>10,13; 13,51</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>9,57; 15,99</t>
+          <t>9,41; 16,43</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>12,47; 16,4</t>
+          <t>12,6; 16,25</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>10,89; 14,13</t>
+          <t>10,87; 13,92</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>10,35; 13,67</t>
+          <t>10,37; 13,92</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>8,67; 20,86</t>
+          <t>8,44; 20,29</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>13,32; 15,63</t>
+          <t>13,26; 15,48</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>11,95; 14,8</t>
+          <t>11,66; 14,59</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>10,49; 13,02</t>
+          <t>10,56; 13,09</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>10,33; 17,8</t>
+          <t>10,03; 17,34</t>
         </is>
       </c>
     </row>
@@ -1556,62 +1556,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>13,58; 14,61</t>
+          <t>13,65; 14,65</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>11,37; 12,44</t>
+          <t>11,31; 12,49</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>11,09; 12,16</t>
+          <t>11,1; 12,08</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>12,01; 16,53</t>
+          <t>12,06; 16,66</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>13,36; 14,42</t>
+          <t>13,34; 14,52</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>11,43; 12,51</t>
+          <t>11,39; 12,47</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>11,31; 12,41</t>
+          <t>11,3; 12,42</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>11,58; 14,27</t>
+          <t>11,45; 14,36</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>13,59; 14,36</t>
+          <t>13,61; 14,36</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>11,54; 12,32</t>
+          <t>11,51; 12,31</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>11,34; 12,12</t>
+          <t>11,33; 12,07</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>12,08; 14,76</t>
+          <t>12,21; 14,78</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/IQ18C_M-Clase-trans_orig.xlsx
+++ b/data/trans_orig/IQ18C_M-Clase-trans_orig.xlsx
@@ -526,13 +526,13 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Tiempo que dura el trayecto desde su domicilio al médico en minutos (tasa de respuesta: 95,27%)</t>
+          <t>Tiempo medio en minutos que dura el trayecto desde su domicilio a la consulta médica (tasa de respuesta: 95,27%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -540,7 +540,7 @@
       <c r="F1" s="3" t="n"/>
       <c r="G1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="H1" s="3" t="n"/>
@@ -648,42 +648,42 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>14,98</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>12,64</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>11,53</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>11,21</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
           <t>15,04</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="H4" s="2" t="inlineStr">
         <is>
           <t>11,73</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="I4" s="2" t="inlineStr">
         <is>
           <t>12,48</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>14,45</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>14,98</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>12,64</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>11,53</t>
-        </is>
-      </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>11,28</t>
+          <t>14,22</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -703,7 +703,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>13,01</t>
+          <t>12,82</t>
         </is>
       </c>
     </row>
@@ -716,62 +716,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>13,81; 16,28</t>
+          <t>13,67; 16,8</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>10,39; 13,39</t>
+          <t>11,6; 14,26</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>11,2; 14,12</t>
+          <t>10,46; 13,18</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>11,87; 18,85</t>
+          <t>9,3; 14,06</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>13,6; 16,72</t>
+          <t>13,97; 16,42</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>11,48; 14,15</t>
+          <t>10,27; 13,44</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>10,51; 13,33</t>
+          <t>11,17; 14,24</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>9,35; 14,38</t>
+          <t>11,37; 18,32</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>14,03; 16,02</t>
+          <t>14,07; 16,08</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>11,21; 13,32</t>
+          <t>11,34; 13,39</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>11,05; 13,07</t>
+          <t>11,05; 13,04</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>11,11; 15,4</t>
+          <t>11,11; 15,3</t>
         </is>
       </c>
     </row>
@@ -788,42 +788,42 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>13,55</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>12,94</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>12,48</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>13,27</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
           <t>14,39</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="H6" s="2" t="inlineStr">
         <is>
           <t>11,57</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="I6" s="2" t="inlineStr">
         <is>
           <t>11,83</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>10,2</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>13,55</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>12,94</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>12,48</t>
-        </is>
-      </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>13,01</t>
+          <t>10,0</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -843,7 +843,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>11,78</t>
+          <t>11,84</t>
         </is>
       </c>
     </row>
@@ -856,62 +856,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>13,25; 15,94</t>
+          <t>12,24; 16,37</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>10,57; 12,97</t>
+          <t>11,51; 15,45</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>10,71; 14,03</t>
+          <t>11,31; 14,32</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>6,77; 14,11</t>
+          <t>10,58; 15,92</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>12,2; 16,2</t>
+          <t>13,17; 15,88</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>11,55; 15,75</t>
+          <t>10,54; 12,89</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>11,31; 14,24</t>
+          <t>10,62; 13,75</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>10,51; 15,86</t>
+          <t>6,99; 14,41</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>13,01; 15,34</t>
+          <t>13,08; 15,42</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>11,33; 13,56</t>
+          <t>11,34; 13,63</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>11,26; 13,49</t>
+          <t>11,16; 13,43</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>9,72; 13,95</t>
+          <t>9,85; 14,22</t>
         </is>
       </c>
     </row>
@@ -928,42 +928,42 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>14,49</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>11,39</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>12,18</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>18,03</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
           <t>13,63</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="H8" s="2" t="inlineStr">
         <is>
           <t>11,73</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="I8" s="2" t="inlineStr">
         <is>
           <t>11,27</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>10,7</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>14,49</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>11,39</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>12,18</t>
-        </is>
-      </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>17,64</t>
+          <t>10,76</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -983,7 +983,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>15,95</t>
+          <t>16,21</t>
         </is>
       </c>
     </row>
@@ -996,62 +996,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>12,47; 14,84</t>
+          <t>13,3; 16,43</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>10,43; 13,68</t>
+          <t>10,08; 13,21</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>10,16; 12,77</t>
+          <t>10,84; 13,77</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>5,57; 14,4</t>
+          <t>12,17; 31,84</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>13,22; 16,42</t>
+          <t>12,53; 14,88</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>10,28; 13,49</t>
+          <t>10,55; 13,56</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>10,89; 13,6</t>
+          <t>10,19; 12,74</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>12,01; 31,48</t>
+          <t>6,03; 14,43</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>13,17; 15,25</t>
+          <t>13,26; 15,26</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>10,65; 12,75</t>
+          <t>10,66; 12,78</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>10,78; 12,81</t>
+          <t>10,85; 12,77</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>11,56; 26,49</t>
+          <t>11,48; 28,02</t>
         </is>
       </c>
     </row>
@@ -1068,42 +1068,42 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>13,27</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>11,16</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>11,45</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>12,94</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
           <t>13,53</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="H10" s="2" t="inlineStr">
         <is>
           <t>12,37</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="I10" s="2" t="inlineStr">
         <is>
           <t>11,36</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>12,42</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>13,27</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>11,16</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>11,45</t>
-        </is>
-      </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>12,78</t>
+          <t>12,79</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1123,7 +1123,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>12,63</t>
+          <t>12,88</t>
         </is>
       </c>
     </row>
@@ -1136,62 +1136,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>12,78; 14,34</t>
+          <t>12,53; 14,02</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>11,41; 13,94</t>
+          <t>10,42; 12,27</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>10,64; 12,38</t>
+          <t>10,63; 12,49</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>9,68; 17,03</t>
+          <t>11,08; 15,2</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>12,52; 14,01</t>
+          <t>12,73; 14,39</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>10,35; 12,23</t>
+          <t>11,29; 13,85</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>10,65; 12,61</t>
+          <t>10,64; 12,25</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>10,93; 15,03</t>
+          <t>9,51; 17,55</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>12,86; 13,98</t>
+          <t>12,86; 14,0</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>11,03; 12,57</t>
+          <t>11,02; 12,56</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>10,83; 12,11</t>
+          <t>10,87; 12,21</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>10,8; 15,06</t>
+          <t>11,08; 15,39</t>
         </is>
       </c>
     </row>
@@ -1208,42 +1208,42 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>13,46</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>12,2</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>11,84</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>11,68</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
           <t>13,8</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="H12" s="2" t="inlineStr">
         <is>
           <t>10,65</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="I12" s="2" t="inlineStr">
         <is>
           <t>11,28</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>17,99</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>13,46</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>12,2</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>11,84</t>
-        </is>
-      </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>11,44</t>
+          <t>18,07</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1263,7 +1263,7 @@
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>14,14</t>
+          <t>14,42</t>
         </is>
       </c>
     </row>
@@ -1276,62 +1276,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>12,55; 16,23</t>
+          <t>12,45; 15,09</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>9,85; 11,64</t>
+          <t>11,11; 14,0</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>10,29; 12,69</t>
+          <t>10,54; 13,59</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>12,6; 29,66</t>
+          <t>9,26; 16,61</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>12,46; 15,11</t>
+          <t>12,5; 16,15</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>11,05; 13,89</t>
+          <t>9,81; 11,69</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>10,52; 13,7</t>
+          <t>10,31; 12,81</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>9,17; 15,39</t>
+          <t>12,34; 30,01</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>12,76; 14,97</t>
+          <t>12,73; 14,92</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>10,68; 12,36</t>
+          <t>10,62; 12,42</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>10,72; 12,6</t>
+          <t>10,76; 12,84</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>11,1; 18,86</t>
+          <t>11,49; 19,36</t>
         </is>
       </c>
     </row>
@@ -1348,42 +1348,42 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>14,17</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>12,12</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>11,69</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>14,51</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
           <t>14,43</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="H14" s="2" t="inlineStr">
         <is>
           <t>14,33</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
+      <c r="I14" s="2" t="inlineStr">
         <is>
           <t>11,5</t>
         </is>
       </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>12,53</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>14,17</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>12,12</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>11,69</t>
-        </is>
-      </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>13,76</t>
+          <t>12,49</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -1403,7 +1403,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>13,21</t>
+          <t>13,54</t>
         </is>
       </c>
     </row>
@@ -1416,62 +1416,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>13,21; 15,87</t>
+          <t>12,57; 16,27</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>12,31; 17,41</t>
+          <t>10,83; 14,1</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>10,13; 13,51</t>
+          <t>10,28; 14,07</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>9,41; 16,43</t>
+          <t>9,46; 23,23</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>12,6; 16,25</t>
+          <t>13,22; 15,93</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>10,87; 13,92</t>
+          <t>12,43; 18,06</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>10,37; 13,92</t>
+          <t>10,17; 13,92</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>8,44; 20,29</t>
+          <t>9,28; 15,66</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>13,26; 15,48</t>
+          <t>13,27; 15,52</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>11,66; 14,59</t>
+          <t>11,89; 14,64</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>10,56; 13,09</t>
+          <t>10,63; 13,16</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>10,03; 17,34</t>
+          <t>10,32; 18,03</t>
         </is>
       </c>
     </row>
@@ -1488,42 +1488,42 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>13,87</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>11,91</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>11,8</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>12,97</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
           <t>14,06</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="H16" s="2" t="inlineStr">
         <is>
           <t>11,88</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
+      <c r="I16" s="2" t="inlineStr">
         <is>
           <t>11,56</t>
         </is>
       </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>13,78</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>13,87</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>11,91</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>11,8</t>
-        </is>
-      </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>12,76</t>
+          <t>13,82</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
@@ -1543,7 +1543,7 @@
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>13,21</t>
+          <t>13,35</t>
         </is>
       </c>
     </row>
@@ -1556,62 +1556,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>13,65; 14,65</t>
+          <t>13,32; 14,48</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>11,31; 12,49</t>
+          <t>11,38; 12,57</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>11,1; 12,08</t>
+          <t>11,28; 12,36</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>12,06; 16,66</t>
+          <t>11,72; 14,84</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>13,34; 14,52</t>
+          <t>13,6; 14,61</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>11,39; 12,47</t>
+          <t>11,38; 12,54</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>11,3; 12,42</t>
+          <t>11,07; 12,13</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>11,45; 14,36</t>
+          <t>12,02; 16,72</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>13,61; 14,36</t>
+          <t>13,58; 14,35</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>11,51; 12,31</t>
+          <t>11,52; 12,3</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>11,33; 12,07</t>
+          <t>11,33; 12,09</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>12,21; 14,78</t>
+          <t>12,31; 14,85</t>
         </is>
       </c>
     </row>
